--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ104"/>
+  <dimension ref="A1:AZ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,45 +1456,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011377</v>
+        <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>93454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästtjärnåsen, Dlr</t>
+          <t>Väg mot Hästtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408995</v>
+        <v>409340</v>
       </c>
       <c r="R9" t="n">
-        <v>6782299</v>
+        <v>6782308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,22 +1532,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,30 +1546,41 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre tallskog. I kanten av en grusväg</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Henrik Liliedahl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Henrik Liliedahl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011377</t>
+          <t>https://artportalen.se/Sighting/137118664</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011378</v>
+        <v>129011377</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1603,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408984</v>
+        <v>408995</v>
       </c>
       <c r="R10" t="n">
-        <v>6782347</v>
+        <v>6782299</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,13 +1686,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011378</t>
+          <t>https://artportalen.se/Sighting/129011377</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011379</v>
+        <v>129011378</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1715,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408991</v>
+        <v>408984</v>
       </c>
       <c r="R11" t="n">
-        <v>6782360</v>
+        <v>6782347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1760,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,13 +1798,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011379</t>
+          <t>https://artportalen.se/Sighting/129011378</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011380</v>
+        <v>129011379</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1827,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408984</v>
+        <v>408991</v>
       </c>
       <c r="R12" t="n">
-        <v>6782385</v>
+        <v>6782360</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,13 +1910,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011380</t>
+          <t>https://artportalen.se/Sighting/129011379</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011381</v>
+        <v>129011380</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1939,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409010</v>
+        <v>408984</v>
       </c>
       <c r="R13" t="n">
-        <v>6782383</v>
+        <v>6782385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,13 +2022,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011381</t>
+          <t>https://artportalen.se/Sighting/129011380</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011383</v>
+        <v>129011381</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -2051,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409028</v>
+        <v>409010</v>
       </c>
       <c r="R14" t="n">
-        <v>6782350</v>
+        <v>6782383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,13 +2134,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011383</t>
+          <t>https://artportalen.se/Sighting/129011381</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011384</v>
+        <v>129011383</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2163,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409068</v>
+        <v>409028</v>
       </c>
       <c r="R15" t="n">
-        <v>6782377</v>
+        <v>6782350</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,13 +2246,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011384</t>
+          <t>https://artportalen.se/Sighting/129011383</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011385</v>
+        <v>129011384</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2275,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409214</v>
+        <v>409068</v>
       </c>
       <c r="R16" t="n">
-        <v>6782345</v>
+        <v>6782377</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2320,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,13 +2358,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011385</t>
+          <t>https://artportalen.se/Sighting/129011384</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129011386</v>
+        <v>129011385</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2387,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409210</v>
+        <v>409214</v>
       </c>
       <c r="R17" t="n">
-        <v>6782365</v>
+        <v>6782345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2422,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2432,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,13 +2470,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011386</t>
+          <t>https://artportalen.se/Sighting/129011385</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011387</v>
+        <v>129011386</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2499,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409232</v>
+        <v>409210</v>
       </c>
       <c r="R18" t="n">
-        <v>6782353</v>
+        <v>6782365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2534,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,13 +2582,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011387</t>
+          <t>https://artportalen.se/Sighting/129011386</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011388</v>
+        <v>129011387</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2611,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409250</v>
+        <v>409232</v>
       </c>
       <c r="R19" t="n">
-        <v>6782354</v>
+        <v>6782353</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2646,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2656,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,13 +2694,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011388</t>
+          <t>https://artportalen.se/Sighting/129011387</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011389</v>
+        <v>129011388</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2723,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409278</v>
+        <v>409250</v>
       </c>
       <c r="R20" t="n">
-        <v>6782361</v>
+        <v>6782354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2768,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,13 +2806,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011389</t>
+          <t>https://artportalen.se/Sighting/129011388</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011390</v>
+        <v>129011389</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2835,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409349</v>
+        <v>409278</v>
       </c>
       <c r="R21" t="n">
-        <v>6782376</v>
+        <v>6782361</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2880,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,13 +2918,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011390</t>
+          <t>https://artportalen.se/Sighting/129011389</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011391</v>
+        <v>129011390</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2950,7 +2962,7 @@
         <v>409349</v>
       </c>
       <c r="R22" t="n">
-        <v>6782383</v>
+        <v>6782376</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3018,13 +3030,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011391</t>
+          <t>https://artportalen.se/Sighting/129011390</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011392</v>
+        <v>129011391</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3059,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409361</v>
+        <v>409349</v>
       </c>
       <c r="R23" t="n">
-        <v>6782401</v>
+        <v>6782383</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3094,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3104,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,13 +3142,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011392</t>
+          <t>https://artportalen.se/Sighting/129011391</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011393</v>
+        <v>129011392</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3171,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409472</v>
+        <v>409361</v>
       </c>
       <c r="R24" t="n">
-        <v>6782351</v>
+        <v>6782401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3206,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3216,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3242,13 +3254,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011393</t>
+          <t>https://artportalen.se/Sighting/129011392</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011394</v>
+        <v>129011393</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3283,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409543</v>
+        <v>409472</v>
       </c>
       <c r="R25" t="n">
-        <v>6782361</v>
+        <v>6782351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,7 +3330,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3328,7 +3340,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,13 +3366,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011394</t>
+          <t>https://artportalen.se/Sighting/129011393</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011395</v>
+        <v>129011394</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3395,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409555</v>
+        <v>409543</v>
       </c>
       <c r="R26" t="n">
-        <v>6782356</v>
+        <v>6782361</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3430,7 +3442,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3440,7 +3452,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,13 +3478,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011395</t>
+          <t>https://artportalen.se/Sighting/129011394</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011396</v>
+        <v>129011395</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3507,10 +3519,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409584</v>
+        <v>409555</v>
       </c>
       <c r="R27" t="n">
-        <v>6782395</v>
+        <v>6782356</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3542,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3552,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3578,13 +3590,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011396</t>
+          <t>https://artportalen.se/Sighting/129011395</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011398</v>
+        <v>129011396</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3619,7 +3631,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409596</v>
+        <v>409584</v>
       </c>
       <c r="R28" t="n">
         <v>6782395</v>
@@ -3654,7 +3666,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3664,7 +3676,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3690,13 +3702,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011398</t>
+          <t>https://artportalen.se/Sighting/129011396</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129011399</v>
+        <v>129011398</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3731,10 +3743,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409609</v>
+        <v>409596</v>
       </c>
       <c r="R29" t="n">
-        <v>6782404</v>
+        <v>6782395</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,7 +3778,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3776,7 +3788,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3802,13 +3814,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011399</t>
+          <t>https://artportalen.se/Sighting/129011398</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011400</v>
+        <v>129011399</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3843,10 +3855,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409643</v>
+        <v>409609</v>
       </c>
       <c r="R30" t="n">
-        <v>6782378</v>
+        <v>6782404</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3878,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3888,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3914,13 +3926,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011400</t>
+          <t>https://artportalen.se/Sighting/129011399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129011401</v>
+        <v>129011400</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3955,10 +3967,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409663</v>
+        <v>409643</v>
       </c>
       <c r="R31" t="n">
-        <v>6782385</v>
+        <v>6782378</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4026,13 +4038,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011401</t>
+          <t>https://artportalen.se/Sighting/129011400</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129011402</v>
+        <v>129011401</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4067,10 +4079,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>409671</v>
+        <v>409663</v>
       </c>
       <c r="R32" t="n">
-        <v>6782390</v>
+        <v>6782385</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4102,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4112,7 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4138,13 +4150,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011402</t>
+          <t>https://artportalen.se/Sighting/129011401</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011403</v>
+        <v>129011402</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4179,10 +4191,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409706</v>
+        <v>409671</v>
       </c>
       <c r="R33" t="n">
-        <v>6782359</v>
+        <v>6782390</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4214,7 +4226,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4224,7 +4236,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,13 +4262,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011403</t>
+          <t>https://artportalen.se/Sighting/129011402</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011404</v>
+        <v>129011403</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4291,10 +4303,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409736</v>
+        <v>409706</v>
       </c>
       <c r="R34" t="n">
-        <v>6782394</v>
+        <v>6782359</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4326,7 +4338,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4348,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4362,13 +4374,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011404</t>
+          <t>https://artportalen.se/Sighting/129011403</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011405</v>
+        <v>129011404</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4403,10 +4415,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409747</v>
+        <v>409736</v>
       </c>
       <c r="R35" t="n">
-        <v>6782328</v>
+        <v>6782394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4438,7 +4450,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4448,7 +4460,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4474,13 +4486,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011405</t>
+          <t>https://artportalen.se/Sighting/129011404</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011406</v>
+        <v>129011405</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4515,10 +4527,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409759</v>
+        <v>409747</v>
       </c>
       <c r="R36" t="n">
-        <v>6782314</v>
+        <v>6782328</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4550,7 +4562,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4560,7 +4572,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4586,13 +4598,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011406</t>
+          <t>https://artportalen.se/Sighting/129011405</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011407</v>
+        <v>129011406</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4627,10 +4639,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409795</v>
+        <v>409759</v>
       </c>
       <c r="R37" t="n">
-        <v>6782327</v>
+        <v>6782314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4662,7 +4674,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4672,7 +4684,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4698,13 +4710,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011407</t>
+          <t>https://artportalen.se/Sighting/129011406</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011408</v>
+        <v>129011407</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4739,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409801</v>
+        <v>409795</v>
       </c>
       <c r="R38" t="n">
-        <v>6782315</v>
+        <v>6782327</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4784,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4810,13 +4822,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011408</t>
+          <t>https://artportalen.se/Sighting/129011407</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011409</v>
+        <v>129011408</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4851,10 +4863,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409202</v>
+        <v>409801</v>
       </c>
       <c r="R39" t="n">
-        <v>6782367</v>
+        <v>6782315</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4886,7 +4898,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4896,7 +4908,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4905,7 +4917,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4923,13 +4934,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011409</t>
+          <t>https://artportalen.se/Sighting/129011408</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032403</v>
+        <v>129011409</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4964,10 +4975,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409021</v>
+        <v>409202</v>
       </c>
       <c r="R40" t="n">
-        <v>6782365</v>
+        <v>6782367</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4997,41 +5008,52 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032403</t>
+          <t>https://artportalen.se/Sighting/129011409</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032405</v>
+        <v>129032403</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5066,7 +5088,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409048</v>
+        <v>409021</v>
       </c>
       <c r="R41" t="n">
         <v>6782365</v>
@@ -5127,13 +5149,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032405</t>
+          <t>https://artportalen.se/Sighting/129032403</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032406</v>
+        <v>129032405</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5168,10 +5190,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409253</v>
+        <v>409048</v>
       </c>
       <c r="R42" t="n">
-        <v>6782372</v>
+        <v>6782365</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5229,13 +5251,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032406</t>
+          <t>https://artportalen.se/Sighting/129032405</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032407</v>
+        <v>129032406</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5270,10 +5292,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409659</v>
+        <v>409253</v>
       </c>
       <c r="R43" t="n">
-        <v>6782436</v>
+        <v>6782372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5331,13 +5353,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032407</t>
+          <t>https://artportalen.se/Sighting/129032406</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032408</v>
+        <v>129032407</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5372,10 +5394,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409749</v>
+        <v>409659</v>
       </c>
       <c r="R44" t="n">
-        <v>6782325</v>
+        <v>6782436</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5433,13 +5455,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032408</t>
+          <t>https://artportalen.se/Sighting/129032407</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032409</v>
+        <v>129032408</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5474,10 +5496,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409782</v>
+        <v>409749</v>
       </c>
       <c r="R45" t="n">
-        <v>6782339</v>
+        <v>6782325</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5535,13 +5557,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032409</t>
+          <t>https://artportalen.se/Sighting/129032408</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032875</v>
+        <v>129032409</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5576,10 +5598,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409034</v>
+        <v>409782</v>
       </c>
       <c r="R46" t="n">
-        <v>6782261</v>
+        <v>6782339</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5626,24 +5648,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032875</t>
+          <t>https://artportalen.se/Sighting/129032409</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032876</v>
+        <v>129032875</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5678,10 +5700,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408997</v>
+        <v>409034</v>
       </c>
       <c r="R47" t="n">
-        <v>6782283</v>
+        <v>6782261</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5739,13 +5761,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032876</t>
+          <t>https://artportalen.se/Sighting/129032875</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032877</v>
+        <v>129032876</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5780,10 +5802,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408994</v>
+        <v>408997</v>
       </c>
       <c r="R48" t="n">
-        <v>6782293</v>
+        <v>6782283</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5841,13 +5863,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032877</t>
+          <t>https://artportalen.se/Sighting/129032876</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032878</v>
+        <v>129032877</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5882,10 +5904,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408966</v>
+        <v>408994</v>
       </c>
       <c r="R49" t="n">
-        <v>6782283</v>
+        <v>6782293</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5943,13 +5965,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032878</t>
+          <t>https://artportalen.se/Sighting/129032877</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032879</v>
+        <v>129032878</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5984,10 +6006,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408909</v>
+        <v>408966</v>
       </c>
       <c r="R50" t="n">
-        <v>6782332</v>
+        <v>6782283</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6045,13 +6067,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032879</t>
+          <t>https://artportalen.se/Sighting/129032878</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032880</v>
+        <v>129032879</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -6086,10 +6108,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408901</v>
+        <v>408909</v>
       </c>
       <c r="R51" t="n">
-        <v>6782390</v>
+        <v>6782332</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6147,13 +6169,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032880</t>
+          <t>https://artportalen.se/Sighting/129032879</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032882</v>
+        <v>129032880</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6188,10 +6210,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408992</v>
+        <v>408901</v>
       </c>
       <c r="R52" t="n">
-        <v>6782394</v>
+        <v>6782390</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6249,13 +6271,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032882</t>
+          <t>https://artportalen.se/Sighting/129032880</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129032883</v>
+        <v>129032882</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -6290,10 +6312,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409010</v>
+        <v>408992</v>
       </c>
       <c r="R53" t="n">
-        <v>6782399</v>
+        <v>6782394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6351,13 +6373,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032883</t>
+          <t>https://artportalen.se/Sighting/129032882</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129032884</v>
+        <v>129032883</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6392,10 +6414,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409039</v>
+        <v>409010</v>
       </c>
       <c r="R54" t="n">
-        <v>6782290</v>
+        <v>6782399</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6453,13 +6475,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032884</t>
+          <t>https://artportalen.se/Sighting/129032883</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129032885</v>
+        <v>129032884</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6494,10 +6516,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409078</v>
+        <v>409039</v>
       </c>
       <c r="R55" t="n">
-        <v>6782312</v>
+        <v>6782290</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6555,13 +6577,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032885</t>
+          <t>https://artportalen.se/Sighting/129032884</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032886</v>
+        <v>129032885</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6596,10 +6618,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409108</v>
+        <v>409078</v>
       </c>
       <c r="R56" t="n">
-        <v>6782395</v>
+        <v>6782312</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6657,13 +6679,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032886</t>
+          <t>https://artportalen.se/Sighting/129032885</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032887</v>
+        <v>129032886</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6698,10 +6720,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409176</v>
+        <v>409108</v>
       </c>
       <c r="R57" t="n">
-        <v>6782420</v>
+        <v>6782395</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6759,13 +6781,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032887</t>
+          <t>https://artportalen.se/Sighting/129032886</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032888</v>
+        <v>129032887</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6800,10 +6822,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409127</v>
+        <v>409176</v>
       </c>
       <c r="R58" t="n">
-        <v>6782290</v>
+        <v>6782420</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6861,13 +6883,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032888</t>
+          <t>https://artportalen.se/Sighting/129032887</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032889</v>
+        <v>129032888</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -6902,10 +6924,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409164</v>
+        <v>409127</v>
       </c>
       <c r="R59" t="n">
-        <v>6782308</v>
+        <v>6782290</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6963,13 +6985,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032889</t>
+          <t>https://artportalen.se/Sighting/129032888</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032890</v>
+        <v>129032889</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7004,10 +7026,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409228</v>
+        <v>409164</v>
       </c>
       <c r="R60" t="n">
-        <v>6782298</v>
+        <v>6782308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7065,13 +7087,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032890</t>
+          <t>https://artportalen.se/Sighting/129032889</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032891</v>
+        <v>129032890</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7106,10 +7128,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409241</v>
+        <v>409228</v>
       </c>
       <c r="R61" t="n">
-        <v>6782372</v>
+        <v>6782298</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7167,13 +7189,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032891</t>
+          <t>https://artportalen.se/Sighting/129032890</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032892</v>
+        <v>129032891</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -7208,10 +7230,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409244</v>
+        <v>409241</v>
       </c>
       <c r="R62" t="n">
-        <v>6782381</v>
+        <v>6782372</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7269,13 +7291,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032892</t>
+          <t>https://artportalen.se/Sighting/129032891</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032893</v>
+        <v>129032892</v>
       </c>
       <c r="B63" t="n">
         <v>79327</v>
@@ -7310,10 +7332,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409280</v>
+        <v>409244</v>
       </c>
       <c r="R63" t="n">
-        <v>6782382</v>
+        <v>6782381</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7371,13 +7393,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032893</t>
+          <t>https://artportalen.se/Sighting/129032892</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032894</v>
+        <v>129032893</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7412,10 +7434,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409292</v>
+        <v>409280</v>
       </c>
       <c r="R64" t="n">
-        <v>6782306</v>
+        <v>6782382</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7473,13 +7495,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032894</t>
+          <t>https://artportalen.se/Sighting/129032893</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032895</v>
+        <v>129032894</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7514,10 +7536,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409310</v>
+        <v>409292</v>
       </c>
       <c r="R65" t="n">
-        <v>6782326</v>
+        <v>6782306</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7575,13 +7597,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032895</t>
+          <t>https://artportalen.se/Sighting/129032894</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032896</v>
+        <v>129032895</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7616,10 +7638,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409331</v>
+        <v>409310</v>
       </c>
       <c r="R66" t="n">
-        <v>6782342</v>
+        <v>6782326</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7677,13 +7699,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032896</t>
+          <t>https://artportalen.se/Sighting/129032895</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032897</v>
+        <v>129032896</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -7718,10 +7740,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409469</v>
+        <v>409331</v>
       </c>
       <c r="R67" t="n">
-        <v>6782371</v>
+        <v>6782342</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7779,13 +7801,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032897</t>
+          <t>https://artportalen.se/Sighting/129032896</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032898</v>
+        <v>129032897</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7820,10 +7842,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409390</v>
+        <v>409469</v>
       </c>
       <c r="R68" t="n">
-        <v>6782289</v>
+        <v>6782371</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7881,13 +7903,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032898</t>
+          <t>https://artportalen.se/Sighting/129032897</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032899</v>
+        <v>129032898</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -7922,10 +7944,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409397</v>
+        <v>409390</v>
       </c>
       <c r="R69" t="n">
-        <v>6782272</v>
+        <v>6782289</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7983,13 +8005,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032899</t>
+          <t>https://artportalen.se/Sighting/129032898</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032900</v>
+        <v>129032899</v>
       </c>
       <c r="B70" t="n">
         <v>79327</v>
@@ -8024,10 +8046,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409449</v>
+        <v>409397</v>
       </c>
       <c r="R70" t="n">
-        <v>6782286</v>
+        <v>6782272</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8085,13 +8107,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032900</t>
+          <t>https://artportalen.se/Sighting/129032899</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032901</v>
+        <v>129032900</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8126,10 +8148,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409528</v>
+        <v>409449</v>
       </c>
       <c r="R71" t="n">
-        <v>6782292</v>
+        <v>6782286</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8187,13 +8209,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032901</t>
+          <t>https://artportalen.se/Sighting/129032900</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032902</v>
+        <v>129032901</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8228,10 +8250,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409549</v>
+        <v>409528</v>
       </c>
       <c r="R72" t="n">
-        <v>6782286</v>
+        <v>6782292</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8289,13 +8311,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032902</t>
+          <t>https://artportalen.se/Sighting/129032901</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032903</v>
+        <v>129032902</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8330,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409582</v>
+        <v>409549</v>
       </c>
       <c r="R73" t="n">
-        <v>6782297</v>
+        <v>6782286</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,13 +8413,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032903</t>
+          <t>https://artportalen.se/Sighting/129032902</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032904</v>
+        <v>129032903</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8432,10 +8454,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409568</v>
+        <v>409582</v>
       </c>
       <c r="R74" t="n">
-        <v>6782383</v>
+        <v>6782297</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8493,13 +8515,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032904</t>
+          <t>https://artportalen.se/Sighting/129032903</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032905</v>
+        <v>129032904</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8534,10 +8556,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409624</v>
+        <v>409568</v>
       </c>
       <c r="R75" t="n">
-        <v>6782292</v>
+        <v>6782383</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8595,13 +8617,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032905</t>
+          <t>https://artportalen.se/Sighting/129032904</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032906</v>
+        <v>129032905</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8636,10 +8658,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409684</v>
+        <v>409624</v>
       </c>
       <c r="R76" t="n">
-        <v>6782322</v>
+        <v>6782292</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8697,13 +8719,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032906</t>
+          <t>https://artportalen.se/Sighting/129032905</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032907</v>
+        <v>129032906</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8738,10 +8760,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409686</v>
+        <v>409684</v>
       </c>
       <c r="R77" t="n">
-        <v>6782351</v>
+        <v>6782322</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8799,13 +8821,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032907</t>
+          <t>https://artportalen.se/Sighting/129032906</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032908</v>
+        <v>129032907</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8840,10 +8862,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409715</v>
+        <v>409686</v>
       </c>
       <c r="R78" t="n">
-        <v>6782363</v>
+        <v>6782351</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8901,13 +8923,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032908</t>
+          <t>https://artportalen.se/Sighting/129032907</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032909</v>
+        <v>129032908</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8942,10 +8964,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409727</v>
+        <v>409715</v>
       </c>
       <c r="R79" t="n">
-        <v>6782352</v>
+        <v>6782363</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9003,13 +9025,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032909</t>
+          <t>https://artportalen.se/Sighting/129032908</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032910</v>
+        <v>129032909</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9044,10 +9066,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409744</v>
+        <v>409727</v>
       </c>
       <c r="R80" t="n">
-        <v>6782394</v>
+        <v>6782352</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9105,13 +9127,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032910</t>
+          <t>https://artportalen.se/Sighting/129032909</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032911</v>
+        <v>129032910</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9146,10 +9168,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409777</v>
+        <v>409744</v>
       </c>
       <c r="R81" t="n">
-        <v>6782445</v>
+        <v>6782394</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9207,13 +9229,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032911</t>
+          <t>https://artportalen.se/Sighting/129032910</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032912</v>
+        <v>129032911</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9248,10 +9270,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>409762</v>
+        <v>409777</v>
       </c>
       <c r="R82" t="n">
-        <v>6782335</v>
+        <v>6782445</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9309,13 +9331,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032912</t>
+          <t>https://artportalen.se/Sighting/129032911</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032913</v>
+        <v>129032912</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9350,10 +9372,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>409757</v>
+        <v>409762</v>
       </c>
       <c r="R83" t="n">
-        <v>6782355</v>
+        <v>6782335</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9411,13 +9433,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032913</t>
+          <t>https://artportalen.se/Sighting/129032912</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032914</v>
+        <v>129032913</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9452,10 +9474,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409759</v>
+        <v>409757</v>
       </c>
       <c r="R84" t="n">
-        <v>6782343</v>
+        <v>6782355</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9513,13 +9535,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032914</t>
+          <t>https://artportalen.se/Sighting/129032913</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032915</v>
+        <v>129032914</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9554,10 +9576,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409765</v>
+        <v>409759</v>
       </c>
       <c r="R85" t="n">
-        <v>6782330</v>
+        <v>6782343</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9615,13 +9637,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032915</t>
+          <t>https://artportalen.se/Sighting/129032914</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032916</v>
+        <v>129032915</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9656,10 +9678,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409812</v>
+        <v>409765</v>
       </c>
       <c r="R86" t="n">
-        <v>6782309</v>
+        <v>6782330</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9717,13 +9739,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032916</t>
+          <t>https://artportalen.se/Sighting/129032915</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032917</v>
+        <v>129032916</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9758,10 +9780,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409360</v>
+        <v>409812</v>
       </c>
       <c r="R87" t="n">
-        <v>6782355</v>
+        <v>6782309</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9819,13 +9841,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032917</t>
+          <t>https://artportalen.se/Sighting/129032916</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032918</v>
+        <v>129032917</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9860,10 +9882,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409363</v>
+        <v>409360</v>
       </c>
       <c r="R88" t="n">
-        <v>6782377</v>
+        <v>6782355</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9921,13 +9943,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032918</t>
+          <t>https://artportalen.se/Sighting/129032917</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032919</v>
+        <v>129032918</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9962,10 +9984,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409358</v>
+        <v>409363</v>
       </c>
       <c r="R89" t="n">
-        <v>6782291</v>
+        <v>6782377</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10023,13 +10045,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032919</t>
+          <t>https://artportalen.se/Sighting/129032918</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129032920</v>
+        <v>129032919</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10064,10 +10086,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409793</v>
+        <v>409358</v>
       </c>
       <c r="R90" t="n">
-        <v>6782448</v>
+        <v>6782291</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10125,38 +10147,38 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032920</t>
+          <t>https://artportalen.se/Sighting/129032919</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129011375</v>
+        <v>129032920</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10166,10 +10188,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409335</v>
+        <v>409793</v>
       </c>
       <c r="R91" t="n">
-        <v>6782352</v>
+        <v>6782448</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10199,19 +10221,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10226,24 +10238,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011375</t>
+          <t>https://artportalen.se/Sighting/129032920</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032872</v>
+        <v>129011375</v>
       </c>
       <c r="B92" t="n">
         <v>79084</v>
@@ -10278,10 +10290,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>409594</v>
+        <v>409335</v>
       </c>
       <c r="R92" t="n">
-        <v>6782294</v>
+        <v>6782352</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10311,9 +10323,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10328,27 +10350,27 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032872</t>
+          <t>https://artportalen.se/Sighting/129011375</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032392</v>
+        <v>129032872</v>
       </c>
       <c r="B93" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10356,21 +10378,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10380,10 +10402,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>409554</v>
+        <v>409594</v>
       </c>
       <c r="R93" t="n">
-        <v>6782380</v>
+        <v>6782294</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10430,27 +10452,27 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032392</t>
+          <t>https://artportalen.se/Sighting/129032872</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129011369</v>
+        <v>129032392</v>
       </c>
       <c r="B94" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10458,42 +10480,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409683</v>
+        <v>409554</v>
       </c>
       <c r="R94" t="n">
-        <v>6782391</v>
+        <v>6782380</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10523,19 +10537,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10550,24 +10554,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011369</t>
+          <t>https://artportalen.se/Sighting/129032392</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129011370</v>
+        <v>129011369</v>
       </c>
       <c r="B95" t="n">
         <v>57953</v>
@@ -10610,10 +10614,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409759</v>
+        <v>409683</v>
       </c>
       <c r="R95" t="n">
-        <v>6782330</v>
+        <v>6782391</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10645,7 +10649,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10655,7 +10659,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10681,13 +10685,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011370</t>
+          <t>https://artportalen.se/Sighting/129011369</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011372</v>
+        <v>129011370</v>
       </c>
       <c r="B96" t="n">
         <v>57953</v>
@@ -10730,10 +10734,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409796</v>
+        <v>409759</v>
       </c>
       <c r="R96" t="n">
-        <v>6782327</v>
+        <v>6782330</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10765,7 +10769,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10775,7 +10779,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10801,13 +10805,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129011372</t>
+          <t>https://artportalen.se/Sighting/129011370</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032395</v>
+        <v>129011372</v>
       </c>
       <c r="B97" t="n">
         <v>57953</v>
@@ -10850,10 +10854,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409759</v>
+        <v>409796</v>
       </c>
       <c r="R97" t="n">
-        <v>6782358</v>
+        <v>6782327</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10883,9 +10887,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10900,24 +10914,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032395</t>
+          <t>https://artportalen.se/Sighting/129011372</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032396</v>
+        <v>129032395</v>
       </c>
       <c r="B98" t="n">
         <v>57953</v>
@@ -10960,10 +10974,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409753</v>
+        <v>409759</v>
       </c>
       <c r="R98" t="n">
-        <v>6782323</v>
+        <v>6782358</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11021,13 +11035,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032396</t>
+          <t>https://artportalen.se/Sighting/129032395</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032866</v>
+        <v>129032396</v>
       </c>
       <c r="B99" t="n">
         <v>57953</v>
@@ -11070,10 +11084,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409757</v>
+        <v>409753</v>
       </c>
       <c r="R99" t="n">
-        <v>6782386</v>
+        <v>6782323</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11120,24 +11134,24 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032866</t>
+          <t>https://artportalen.se/Sighting/129032396</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032867</v>
+        <v>129032866</v>
       </c>
       <c r="B100" t="n">
         <v>57953</v>
@@ -11180,10 +11194,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409693</v>
+        <v>409757</v>
       </c>
       <c r="R100" t="n">
-        <v>6782357</v>
+        <v>6782386</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11241,13 +11255,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032867</t>
+          <t>https://artportalen.se/Sighting/129032866</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129032868</v>
+        <v>129032867</v>
       </c>
       <c r="B101" t="n">
         <v>57953</v>
@@ -11290,10 +11304,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409688</v>
+        <v>409693</v>
       </c>
       <c r="R101" t="n">
-        <v>6782303</v>
+        <v>6782357</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11351,13 +11365,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032868</t>
+          <t>https://artportalen.se/Sighting/129032867</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129032869</v>
+        <v>129032868</v>
       </c>
       <c r="B102" t="n">
         <v>57953</v>
@@ -11400,10 +11414,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409754</v>
+        <v>409688</v>
       </c>
       <c r="R102" t="n">
-        <v>6782356</v>
+        <v>6782303</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11461,16 +11475,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032869</t>
+          <t>https://artportalen.se/Sighting/129032868</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129032393</v>
+        <v>129032869</v>
       </c>
       <c r="B103" t="n">
-        <v>79917</v>
+        <v>57953</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11478,34 +11492,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409554</v>
+        <v>409754</v>
       </c>
       <c r="R103" t="n">
-        <v>6782380</v>
+        <v>6782356</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11552,24 +11574,24 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129032393</t>
+          <t>https://artportalen.se/Sighting/129032869</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032394</v>
+        <v>129032393</v>
       </c>
       <c r="B104" t="n">
         <v>79917</v>
@@ -11604,10 +11626,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409553</v>
+        <v>409554</v>
       </c>
       <c r="R104" t="n">
-        <v>6782378</v>
+        <v>6782380</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11664,6 +11686,108 @@
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032393</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129032394</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Hästtjärnåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>409553</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6782378</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129032394</t>
         </is>
@@ -11774,6 +11898,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>137118664</v>
       </c>
       <c r="B9" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
